--- a/spreadsheet/数据表.xlsx
+++ b/spreadsheet/数据表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willowfitzgerald/REBEL GAME/AnovelCnPGame/spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE0C3CB-D6B1-3948-AF33-BD0661686DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A573FE4F-19DD-CA46-AD71-091DBEB5B9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{044061C3-F085-2646-8EEC-6890BA2084EC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
   <si>
     <t>真相卡</t>
   </si>
@@ -147,6 +147,213 @@
   </si>
   <si>
     <t>谁是内鬼</t>
+  </si>
+  <si>
+    <t>看星盘</t>
+  </si>
+  <si>
+    <t>书记员</t>
+  </si>
+  <si>
+    <t>不理解无名者</t>
+  </si>
+  <si>
+    <t>器官移植</t>
+  </si>
+  <si>
+    <t>研究课题</t>
+  </si>
+  <si>
+    <t>免费咖啡</t>
+  </si>
+  <si>
+    <t>过节</t>
+  </si>
+  <si>
+    <t>他认为一定是外星人赐予了高层长寿。每次都问你要不要看个星盘？收费500。</t>
+  </si>
+  <si>
+    <t>情绪化</t>
+  </si>
+  <si>
+    <t>他总是昼伏夜出，且每次都神神叨叨的，情绪很不稳定的样子。有一次他自言自语地来参与会议，差点撞柱子上</t>
+  </si>
+  <si>
+    <t>她干了一辈子书记员，打字都快打不明白了还在当书记员。她总是炫耀说自己很快就能当上法官了，然而却总是事与愿违。</t>
+  </si>
+  <si>
+    <t>蹲守地库</t>
+  </si>
+  <si>
+    <t>通过监控，好友发现，有个身影每周都会鬼鬼祟祟地蹲在地库前，并且不断踱步徘徊，行为举止相当可疑。原来，此人就是候补法官。</t>
+  </si>
+  <si>
+    <t>公开地址</t>
+  </si>
+  <si>
+    <t>公开地址之前直播的时候，他将无名者的线下会面地址直接打在直播间里招新。</t>
+  </si>
+  <si>
+    <t>这个年纪轻轻就有百万粉丝的游戏主播总是在你们开会的时候不停地提问，“为什么你们要做这些？为什么你们要做那些？”</t>
+  </si>
+  <si>
+    <t>认为高层一定在移植器官，所谓的医疗技术其实根本没有实现，只是牺牲底层人民性命换取长寿的谎言罢了。</t>
+  </si>
+  <si>
+    <t>缺席会议</t>
+  </si>
+  <si>
+    <t>值得一提的是，从未缺席过讨论会的他，前两周都缺席了。</t>
+  </si>
+  <si>
+    <t>他是个失业的博士，正在研究“失业经济对哲学发展的影响”。目前，他正在等待自己的研究课题被通过。</t>
+  </si>
+  <si>
+    <t>意外之财</t>
+  </si>
+  <si>
+    <t>通过调查，你们发现这位失业哲学博士的银行卡上突然多了一笔巨款，而且时间正好是爆炸案前一天。</t>
+  </si>
+  <si>
+    <t>他来这里是因为每天都能喝免费咖啡</t>
+  </si>
+  <si>
+    <t>也许，最一开始，就是好友举报了你呢？</t>
+  </si>
+  <si>
+    <t>录音机</t>
+  </si>
+  <si>
+    <t>某次会议结束之后，你留意到她正在摆弄一个录音机，并且偷偷藏了起来。</t>
+  </si>
+  <si>
+    <t>经济</t>
+  </si>
+  <si>
+    <t>37岁职业占星师</t>
+  </si>
+  <si>
+    <t>59岁候补法官</t>
+  </si>
+  <si>
+    <t>13岁游戏主播</t>
+  </si>
+  <si>
+    <t>阴谋论播客主持人</t>
+  </si>
+  <si>
+    <t>42岁失业哲学博士</t>
+  </si>
+  <si>
+    <t>牙医</t>
+  </si>
+  <si>
+    <t>谁举报了无名者？</t>
+  </si>
+  <si>
+    <t>保守党领袖</t>
+  </si>
+  <si>
+    <t>身为保守党领袖的Anta，一直以来都是你母亲最大的政敌。</t>
+  </si>
+  <si>
+    <t>首相竞选</t>
+  </si>
+  <si>
+    <t>下个月就是全民公开首相大选了，你母亲出局后Anta就是最大的赢家。</t>
+  </si>
+  <si>
+    <t>言论攻击1</t>
+  </si>
+  <si>
+    <t>你母亲作为创新党领袖纵容自己女儿的恐怖组织“无名者”。</t>
+  </si>
+  <si>
+    <t>言论攻击2</t>
+  </si>
+  <si>
+    <t>创新党内部组织架构腐败，不少人徇私枉法。</t>
+  </si>
+  <si>
+    <t>言论攻击3</t>
+  </si>
+  <si>
+    <t>创新党联系外星人，想要毁灭地球文明。</t>
+  </si>
+  <si>
+    <t>创新党领袖</t>
+  </si>
+  <si>
+    <t>无名者的存在会令创新党备受非议。</t>
+  </si>
+  <si>
+    <t>恨铁不成钢</t>
+  </si>
+  <si>
+    <t>你母亲从未对你抱有任何期望，她兴许是最早举报你的人。</t>
+  </si>
+  <si>
+    <t>采访</t>
+  </si>
+  <si>
+    <t>记者向你母亲提问：您相信自己的女儿吗？你母亲回答：法律会给出答案。</t>
+  </si>
+  <si>
+    <t>童年回忆</t>
+  </si>
+  <si>
+    <t>她永远在电视上，从不在家里。她记得国家预算却不记得你的生日，她记得议会投票时间却不记得你的毕业典礼。</t>
+  </si>
+  <si>
+    <t>退租</t>
+  </si>
+  <si>
+    <t>你们曾经租过一个工作室，场地非常大但是也很贵，后来由于资金有限被迫选了现在的地址。</t>
+  </si>
+  <si>
+    <t>邪教组织</t>
+  </si>
+  <si>
+    <t>工作室的租期一到前房东就迫不及待地想要将你们赶走，他非常后悔租给你们，觉得“无名者”就是个邪教组织。</t>
+  </si>
+  <si>
+    <t>邋遢</t>
+  </si>
+  <si>
+    <t>他每次都骂骂咧咧地来打扫卫生，说你们实在是太邋遢了，烟头啤酒瓶乱丢。</t>
+  </si>
+  <si>
+    <t>胡闹</t>
+  </si>
+  <si>
+    <t>走私物</t>
+  </si>
+  <si>
+    <t>你们在他的船上发现了大量的走私物，这就是他的谋生手段。</t>
+  </si>
+  <si>
+    <t>前成员</t>
+  </si>
+  <si>
+    <t>船长曾是“无名者”的一员。</t>
+  </si>
+  <si>
+    <t>他发现说好的每周轮流负责结果只有他自己在认真，于是他便退出“无名者”，他说自己真的需要去赚钱不能胡闹了。</t>
+  </si>
+  <si>
+    <t>船长</t>
+  </si>
+  <si>
+    <t>Anta</t>
+  </si>
+  <si>
+    <t>母亲</t>
+  </si>
+  <si>
+    <t>前房东</t>
+  </si>
+  <si>
+    <t>保洁员</t>
   </si>
 </sst>
 </file>
@@ -525,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC16905-D88F-6F45-8481-AD0F8B4B1842}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -691,6 +898,405 @@
       <c r="A9" t="s">
         <v>35</v>
       </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/spreadsheet/数据表.xlsx
+++ b/spreadsheet/数据表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willowfitzgerald/REBEL GAME/AnovelCnPGame/spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A573FE4F-19DD-CA46-AD71-091DBEB5B9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCB6844-31E4-014B-A402-2D25383DF254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{044061C3-F085-2646-8EEC-6890BA2084EC}"/>
   </bookViews>
@@ -1300,5 +1300,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>